--- a/enrollment/002_psa_form--enrollment.xlsx
+++ b/enrollment/002_psa_form--enrollment.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Kid Date Of Birth</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Assessment Level</t>
+          <t>Kid Assessment Level</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Medical Conditions</t>
+          <t>Kid Medical Conditions</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Media Declaration</t>
+          <t>Kid Media Declaration</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Terms and Conditions</t>
+          <t>Kid Terms Conditions</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Agree</t>
+          <t>Kid Agree</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Kid Submit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Terms and Conditions</t>
+          <t>Kid Terms</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>kid_terms_conditions</t>
+          <t>kid_terms_conditions_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Terms and Conditions</t>
+          <t>Kid Terms Conditions 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1055,9 +1055,9 @@
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'enrollment'}</t>
+          <t>enrollment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Enrollment'}</t>
+          <t>Enrollment</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cancel'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Cancel'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1442,46 +1442,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cancel'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Cancel'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kid_terms_conditions_choices</t>
+          <t>kid_terms_conditions_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kid_terms_conditions_choices</t>
+          <t>kid_terms_conditions_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
